--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -69,7 +69,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Жанааркинский район Сарыарка  д 6  кв 1</t>
+    <t xml:space="preserve">Жанааркинский район {documentAddress}</t>
   </si>
   <si>
     <t xml:space="preserve">ИИК поставщика:KZ26601A171001246741,АО «Народный Банк Казахстана» HSBKKZKX</t>
